--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:52</t>
+    <t xml:space="preserve">2026-09-10 01:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:03</t>
+    <t xml:space="preserve">2026-09-18 11:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:10</t>
+    <t xml:space="preserve">2026-09-23 14:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:33</t>
+    <t xml:space="preserve">2026-10-02 16:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2021_biobio.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Chiguayante</t>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Negrete</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:14</t>
+    <t xml:space="preserve">2026-10-04 10:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:21</t>
+    <t xml:space="preserve">2026-10-05 15:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
